--- a/output/pdf_financials_xlsx/GWAY.xlsx
+++ b/output/pdf_financials_xlsx/GWAY.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.703194</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.16109</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.16109</v>
       </c>
     </row>
     <row r="93">
@@ -3179,7 +3179,11 @@
           <t>Warrants reserve 15</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.16569</v>
       </c>
@@ -3206,7 +3210,11 @@
           <t>Share-based payments reserve 14</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>5.537504</v>
       </c>

--- a/output/pdf_financials_xlsx/GWAY.xlsx
+++ b/output/pdf_financials_xlsx/GWAY.xlsx
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.642109</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.53081</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.142898</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.642109</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.53081</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.142898</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.107438</v>
+        <v>0.465329</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.100851</v>
+        <v>0.570041</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.913576</v>
+        <v>0.770678</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">

--- a/output/pdf_financials_xlsx/GWAY.xlsx
+++ b/output/pdf_financials_xlsx/GWAY.xlsx
@@ -3092,7 +3092,11 @@
           <t>Lease liabilities 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>8.666722999999999</v>
       </c>
